--- a/rates-nodispo/week-19/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-19/Analisis_Rates_NoDispo_7d.xlsx
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14477,7 +14477,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14944,7 +14944,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19597,7 +19597,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21950,7 +21950,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23793,7 +23793,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -25636,7 +25636,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28769,7 +28769,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28922,7 +28922,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29083,7 +29083,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -31691,7 +31691,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33737,7 +33737,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36247,7 +36247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38600,7 +38600,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40443,7 +40443,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42286,7 +42286,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45951,7 +45951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48303,7 +48303,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -50192,7 +50192,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -52191,7 +52191,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -54190,7 +54190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-19/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-19/Analisis_Rates_NoDispo_7d.xlsx
@@ -563,14 +563,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P80 · 19496 hoteles · target &lt;3%</t>
+          <t>P80 · 18484 hoteles · target &lt;3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.0006668034468608945</v>
+        <v>0.0007033109716511577</v>
       </c>
     </row>
     <row r="7">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01487484612228149</v>
+        <v>0.01563514390824497</v>
       </c>
     </row>
     <row r="8">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1661</v>
+        <v>1657</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.08519696347968814</v>
+        <v>0.08964509846353604</v>
       </c>
     </row>
     <row r="9">
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1270</v>
+        <v>1210</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06514156750102586</v>
+        <v>0.06546202120753083</v>
       </c>
     </row>
     <row r="10">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>16262</v>
+        <v>15315</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8341198194501436</v>
+        <v>0.828554425449037</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +723,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.001203369434416366</v>
+        <v>0.001222493887530562</v>
       </c>
     </row>
     <row r="7">
@@ -782,7 +782,7 @@
         <v>212</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.02834603556625217</v>
+        <v>0.02879652268405325</v>
       </c>
     </row>
     <row r="8">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1079</v>
+        <v>1063</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1442706244150287</v>
+        <v>0.1443901113827764</v>
       </c>
     </row>
     <row r="9">
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.08316619868966439</v>
+        <v>0.08408041293126868</v>
       </c>
     </row>
     <row r="10">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>5557</v>
+        <v>5459</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.7430137718946384</v>
+        <v>0.7415104591143711</v>
       </c>
     </row>
   </sheetData>
@@ -876,7 +876,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>6984</v>
+        <v>6872</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.9338146811070999</v>
+        <v>0.9334419994566694</v>
       </c>
     </row>
     <row r="8">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.01657975665195882</v>
+        <v>0.01657158380874762</v>
       </c>
     </row>
     <row r="9">
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.02059098810001337</v>
+        <v>0.02078239608801956</v>
       </c>
     </row>
     <row r="10">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.02901457414092793</v>
+        <v>0.02920402064656344</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1037,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14477,7 +14477,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14518,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.0008125834349062627</v>
+        <v>0.0008439836026042923</v>
       </c>
     </row>
     <row r="7">
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01329154332810958</v>
+        <v>0.01374487581384133</v>
       </c>
     </row>
     <row r="8">
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.07069475883684485</v>
+        <v>0.07318543525440077</v>
       </c>
     </row>
     <row r="9">
@@ -14569,10 +14569,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.05078646468164142</v>
+        <v>0.05184470701712081</v>
       </c>
     </row>
     <row r="10">
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>14893</v>
+        <v>14272</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8644146497184979</v>
+        <v>0.8603809983120327</v>
       </c>
     </row>
   </sheetData>
@@ -14630,7 +14630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14686,10 +14686,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>13454</v>
+        <v>12890</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7808926809449185</v>
+        <v>0.7770677598263805</v>
       </c>
     </row>
     <row r="8">
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1137</v>
+        <v>1089</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.06599338324917291</v>
+        <v>0.0656498673740053</v>
       </c>
     </row>
     <row r="9">
@@ -14722,10 +14722,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1218</v>
+        <v>1196</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.07069475883684485</v>
+        <v>0.07210031347962383</v>
       </c>
     </row>
     <row r="10">
@@ -14740,10 +14740,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1420</v>
+        <v>1413</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.08241917696906378</v>
+        <v>0.08518205931999036</v>
       </c>
     </row>
   </sheetData>
@@ -14776,14 +14776,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P80 · 19496 hoteles · target ≥ $650</t>
+          <t>P80 · 18484 hoteles · target ≥ $650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14839,10 +14839,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>14369</v>
+        <v>13579</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7370229790726303</v>
+        <v>0.7346353603116209</v>
       </c>
     </row>
     <row r="8">
@@ -14857,10 +14857,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1916</v>
+        <v>1728</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.09827656955272876</v>
+        <v>0.09348625838563082</v>
       </c>
     </row>
     <row r="9">
@@ -14875,10 +14875,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1666</v>
+        <v>1651</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.08545342634386541</v>
+        <v>0.08932049339969704</v>
       </c>
     </row>
     <row r="10">
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1545</v>
+        <v>1526</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.07924702503077555</v>
+        <v>0.08255788790305128</v>
       </c>
     </row>
   </sheetData>
@@ -14944,7 +14944,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19597,7 +19597,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21950,7 +21950,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23793,7 +23793,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -25636,7 +25636,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28749,7 +28749,7 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28769,7 +28769,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.0007914175167077031</v>
+        <v>0.000856775667571041</v>
       </c>
     </row>
     <row r="7">
@@ -28825,10 +28825,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01521280337671474</v>
+        <v>0.01642153362844495</v>
       </c>
     </row>
     <row r="8">
@@ -28843,10 +28843,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1842</v>
+        <v>1765</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.08098839254308829</v>
+        <v>0.0840116140701604</v>
       </c>
     </row>
     <row r="9">
@@ -28861,10 +28861,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1486</v>
+        <v>1389</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06533591276820261</v>
+        <v>0.06611452234756533</v>
       </c>
     </row>
     <row r="10">
@@ -28879,10 +28879,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>19052</v>
+        <v>17492</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8376714737952866</v>
+        <v>0.8325955542862583</v>
       </c>
     </row>
   </sheetData>
@@ -28902,7 +28902,7 @@
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28922,7 +28922,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28978,10 +28978,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>18956</v>
+        <v>17433</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.8334505803728456</v>
+        <v>0.8297872340425532</v>
       </c>
     </row>
     <row r="8">
@@ -28996,10 +28996,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>533</v>
+        <v>458</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.02343475202251143</v>
+        <v>0.02180018087486315</v>
       </c>
     </row>
     <row r="9">
@@ -29014,10 +29014,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1016</v>
+        <v>918</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.04467112205416813</v>
+        <v>0.04369555904612309</v>
       </c>
     </row>
     <row r="10">
@@ -29032,10 +29032,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2239</v>
+        <v>2200</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.09844354555047485</v>
+        <v>0.1047170260364606</v>
       </c>
     </row>
   </sheetData>
@@ -29083,7 +29083,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -31691,7 +31691,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33737,7 +33737,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36247,7 +36247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38600,7 +38600,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40443,7 +40443,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42286,7 +42286,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45951,7 +45951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48303,7 +48303,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -50192,7 +50192,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -52191,7 +52191,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -54190,7 +54190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56186,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 17:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56324,7 +56324,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Plan saneamiento 303 hoteles Crítica/Súper Crítica</t>
+          <t>Plan saneamiento 302 hoteles Crítica/Súper Crítica</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">

--- a/rates-nodispo/week-19/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-19/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8045,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9888,7 +9888,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14479,7 +14479,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14785,7 +14785,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14946,7 +14946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17554,7 +17554,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19599,7 +19599,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21952,7 +21952,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23795,7 +23795,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -25638,7 +25638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28771,7 +28771,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28924,7 +28924,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29085,7 +29085,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -31693,7 +31693,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33740,7 +33740,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38858,7 +38858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40701,7 +40701,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42544,7 +42544,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -46209,7 +46209,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48561,7 +48561,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -50450,7 +50450,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -52449,7 +52449,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -54448,7 +54448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56444,7 +56444,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
